--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -131,9 +131,6 @@
     <t>PERALTA CRISTOBAL TRISTAN YABAL</t>
   </si>
   <si>
-    <t>PUGA CABRERA ELIAS</t>
-  </si>
-  <si>
     <t>ROSAS SERRANO CRISTOPHER</t>
   </si>
   <si>
@@ -203,15 +200,15 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -251,10 +248,163 @@
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ISMAEL</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>GUSTAVO URIEL</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>PELLICO</t>
+    <t>PUGA CABRERA</t>
   </si>
   <si>
     <t>ROSAS</t>
@@ -263,250 +413,97 @@
     <t>RUIZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
   </si>
   <si>
     <t>CAZARES</t>
   </si>
   <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>SERRANO</t>
   </si>
   <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>JOSE RAMON</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
   </si>
   <si>
     <t>JOSE ALONSO</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ISMAEL</t>
+    <t>VECKA</t>
+  </si>
+  <si>
+    <t>GERSON</t>
+  </si>
+  <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>FATIMA YAMILET</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
   </si>
   <si>
     <t>TRISTAN YABAL</t>
   </si>
   <si>
-    <t>JESUS IVAN</t>
+    <t>ELIAS</t>
   </si>
   <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
     <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>GUSTAVO URIEL</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PUGA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>JOSE RAMON</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>VECKA</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>FATIMA YAMILET</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
   </si>
   <si>
     <t>ARLETT</t>
@@ -870,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1016,16 +1013,16 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1093,16 +1090,16 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1170,16 +1167,16 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1206,16 +1203,16 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1238,7 +1235,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -1247,16 +1244,16 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1289,10 +1286,10 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>-1</v>
@@ -1312,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1324,16 +1321,16 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1360,16 +1357,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1401,16 +1398,16 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1443,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1466,10 +1463,10 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1478,16 +1475,16 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1514,16 +1511,16 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1555,16 +1552,16 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1632,16 +1629,16 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1668,13 +1665,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1709,16 +1706,16 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1745,16 +1742,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1786,16 +1783,16 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1863,16 +1860,16 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1899,7 +1896,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1908,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1940,16 +1937,16 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1982,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2005,7 +2002,7 @@
         <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -2017,16 +2014,16 @@
         <v>-1</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2059,10 +2056,10 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2082,10 +2079,10 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -2100,10 +2097,10 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2136,10 +2133,10 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2159,10 +2156,10 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2171,16 +2168,16 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2207,16 +2204,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2236,10 +2233,10 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>7</v>
@@ -2248,16 +2245,16 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2284,16 +2281,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2313,10 +2310,10 @@
         <v>-1</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2325,16 +2322,16 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2361,16 +2358,16 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2402,16 +2399,16 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2438,16 +2435,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2479,16 +2476,16 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2521,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2556,16 +2553,16 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2592,13 +2589,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2624,7 +2621,7 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -2633,16 +2630,16 @@
         <v>-1</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2669,7 +2666,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2678,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2698,10 +2695,10 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2716,10 +2713,10 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2752,10 +2749,10 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2775,10 +2772,10 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2787,16 +2784,16 @@
         <v>-1</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2823,16 +2820,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2855,7 +2852,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -2864,16 +2861,16 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2909,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2923,7 +2920,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -2932,25 +2929,25 @@
         <v>6</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2977,22 +2974,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3000,34 +2997,34 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>6</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3054,19 +3051,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3077,34 +3074,34 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>6</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3131,22 +3128,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3154,34 +3151,34 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3208,22 +3205,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3231,22 +3228,22 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3255,10 +3252,10 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3285,22 +3282,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>-1</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3308,34 +3305,34 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3362,22 +3359,22 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3385,34 +3382,34 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>10</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35">
         <v>6</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3439,22 +3436,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>10</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3462,16 +3459,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>6</v>
@@ -3480,16 +3477,16 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3519,13 +3516,13 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3539,19 +3536,19 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="D37">
         <v>6</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G37">
         <v>-1</v>
@@ -3566,7 +3563,7 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -3593,19 +3590,19 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="V37">
         <v>6</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>-1</v>
@@ -3616,34 +3613,34 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>-1</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>-1</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -3670,19 +3667,19 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -3693,13 +3690,13 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="C39">
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -3717,10 +3714,10 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>-1</v>
@@ -3747,13 +3744,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="U39">
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -3770,34 +3767,34 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>7</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3824,22 +3821,22 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>7</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3847,22 +3844,22 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="H41">
         <v>-1</v>
@@ -3871,10 +3868,10 @@
         <v>-1</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>-1</v>
@@ -3901,98 +3898,21 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y41">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42">
-        <v>-1</v>
-      </c>
-      <c r="C42">
-        <v>6</v>
-      </c>
-      <c r="D42">
-        <v>-1</v>
-      </c>
-      <c r="E42">
-        <v>-1</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-      <c r="H42">
-        <v>-1</v>
-      </c>
-      <c r="I42">
-        <v>-1</v>
-      </c>
-      <c r="J42">
-        <v>-1</v>
-      </c>
-      <c r="K42">
-        <v>-1</v>
-      </c>
-      <c r="L42">
-        <v>-1</v>
-      </c>
-      <c r="M42">
-        <v>-1</v>
-      </c>
-      <c r="N42">
-        <v>-1</v>
-      </c>
-      <c r="O42">
-        <v>-1</v>
-      </c>
-      <c r="P42">
-        <v>-1</v>
-      </c>
-      <c r="Q42">
-        <v>-1</v>
-      </c>
-      <c r="R42">
-        <v>-1</v>
-      </c>
-      <c r="S42">
-        <v>-1</v>
-      </c>
-      <c r="T42">
-        <v>-1</v>
-      </c>
-      <c r="U42">
-        <v>6</v>
-      </c>
-      <c r="V42">
-        <v>-1</v>
-      </c>
-      <c r="W42">
-        <v>-1</v>
-      </c>
-      <c r="X42">
-        <v>8</v>
-      </c>
-      <c r="Y42">
         <v>-1</v>
       </c>
     </row>
@@ -4020,31 +3940,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4052,7 +3972,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>39</v>
@@ -4081,10 +4001,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>39</v>
@@ -4093,86 +4013,86 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>58.97</v>
       </c>
       <c r="G3">
+        <v>41.03</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I3">
-        <v>16</v>
-      </c>
       <c r="J3">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.97</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>41.03</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5">
         <v>39</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>82.05</v>
+      </c>
+      <c r="G5">
+        <v>17.95</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>9.1</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>28.21</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4180,7 +4100,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6">
         <v>39</v>
@@ -4198,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -4212,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -4246,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4255,16 +4175,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4275,22 +4195,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920181</v>
+        <v>22330051920389</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4298,590 +4218,590 @@
         <v>22330051920389</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920389</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920389</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920389</v>
+        <v>22330051920413</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920190</v>
+        <v>22330051920413</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920190</v>
+        <v>22330051920413</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920190</v>
+        <v>22330051920388</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920413</v>
+        <v>22330051920388</v>
       </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920413</v>
+        <v>21330051920265</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920413</v>
+        <v>21330051920265</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920413</v>
+        <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920413</v>
+        <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920388</v>
+        <v>22330051920193</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920388</v>
+        <v>22330051920194</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
         <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920388</v>
+        <v>22330051920194</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920388</v>
+        <v>22330051920194</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920265</v>
+        <v>22330051920195</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
         <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920265</v>
+        <v>22330051920180</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920265</v>
+        <v>22330051920363</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920265</v>
+        <v>22330051920390</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920378</v>
+        <v>22330051920199</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920359</v>
+        <v>22330051920391</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920359</v>
+        <v>22330051920391</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920359</v>
+        <v>22330051920391</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920193</v>
+        <v>22330051920391</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920193</v>
+        <v>22330051920200</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
         <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920194</v>
+        <v>22330051920371</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920194</v>
+        <v>22330051920371</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920194</v>
+        <v>22330051920371</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920194</v>
+        <v>22330051920201</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>119</v>
@@ -4890,18 +4810,18 @@
         <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920194</v>
+        <v>22330051920201</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>119</v>
@@ -4910,44 +4830,44 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920196</v>
+        <v>22330051920202</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920195</v>
+        <v>22330051920202</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
         <v>61</v>
@@ -4955,30 +4875,30 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>22330051920195</v>
+        <v>22330051920202</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>22330051920195</v>
+        <v>22330051920204</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
         <v>101</v>
@@ -4987,670 +4907,30 @@
         <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>22330051920358</v>
+        <v>22330051920204</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920356</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920180</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>124</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920180</v>
-      </c>
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920363</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920390</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920390</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920199</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920199</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920391</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920391</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>128</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920391</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>128</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920391</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920391</v>
-      </c>
-      <c r="B51" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920391</v>
-      </c>
-      <c r="B52" t="s">
-        <v>85</v>
-      </c>
-      <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920200</v>
-      </c>
-      <c r="B53" t="s">
-        <v>86</v>
-      </c>
-      <c r="C53" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" t="s">
-        <v>129</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920200</v>
-      </c>
-      <c r="B54" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" t="s">
-        <v>129</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920371</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" t="s">
-        <v>130</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920371</v>
-      </c>
-      <c r="B56" t="s">
-        <v>87</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>130</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920371</v>
-      </c>
-      <c r="B57" t="s">
-        <v>87</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" t="s">
-        <v>130</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920371</v>
-      </c>
-      <c r="B58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" t="s">
-        <v>130</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920371</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920201</v>
-      </c>
-      <c r="B60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" t="s">
-        <v>131</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920201</v>
-      </c>
-      <c r="B61" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D61" t="s">
-        <v>131</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920201</v>
-      </c>
-      <c r="B62" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" t="s">
-        <v>106</v>
-      </c>
-      <c r="D62" t="s">
-        <v>131</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920202</v>
-      </c>
-      <c r="B63" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" t="s">
-        <v>106</v>
-      </c>
-      <c r="D63" t="s">
-        <v>132</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920202</v>
-      </c>
-      <c r="B64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" t="s">
-        <v>132</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920202</v>
-      </c>
-      <c r="B65" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" t="s">
-        <v>132</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920202</v>
-      </c>
-      <c r="B66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" t="s">
-        <v>106</v>
-      </c>
-      <c r="D66" t="s">
-        <v>132</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920204</v>
-      </c>
-      <c r="B67" t="s">
-        <v>89</v>
-      </c>
-      <c r="C67" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" t="s">
-        <v>133</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920204</v>
-      </c>
-      <c r="B68" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" t="s">
-        <v>109</v>
-      </c>
-      <c r="D68" t="s">
-        <v>133</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920204</v>
-      </c>
-      <c r="B69" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" t="s">
-        <v>109</v>
-      </c>
-      <c r="D69" t="s">
-        <v>133</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920204</v>
-      </c>
-      <c r="B70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" t="s">
-        <v>109</v>
-      </c>
-      <c r="D70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5669,19 +4949,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5689,16 +4969,16 @@
         <v>22330051920391</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5706,16 +4986,16 @@
         <v>22330051920413</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5723,16 +5003,16 @@
         <v>22330051920194</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5740,169 +5020,169 @@
         <v>22330051920371</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920389</v>
+        <v>22330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920388</v>
+        <v>22330051920389</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920265</v>
+        <v>22330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920202</v>
+        <v>22330051920388</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920204</v>
+        <v>21330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920190</v>
+        <v>22330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920359</v>
+        <v>22330051920204</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920195</v>
+        <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920201</v>
+        <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5910,98 +5190,98 @@
         <v>22330051920193</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920180</v>
+        <v>22330051920195</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920390</v>
+        <v>22330051920180</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920199</v>
+        <v>22330051920363</v>
       </c>
       <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
         <v>84</v>
       </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920200</v>
+        <v>22330051920390</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920181</v>
+        <v>22330051920199</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6009,16 +5289,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920378</v>
+        <v>22330051920200</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6026,84 +5306,84 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920196</v>
+        <v>22330051920177</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920358</v>
+        <v>22330051920178</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920356</v>
+        <v>22330051920179</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920363</v>
+        <v>22330051920181</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920177</v>
+        <v>22330051920182</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6111,16 +5391,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920178</v>
+        <v>22330051920183</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6128,16 +5408,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920179</v>
+        <v>22330051920184</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6145,16 +5425,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920182</v>
+        <v>22330051920185</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6162,16 +5442,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920183</v>
+        <v>22330051920186</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6179,16 +5459,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920184</v>
+        <v>22330051920188</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6196,16 +5476,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920185</v>
+        <v>22330051920187</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6213,16 +5493,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920186</v>
+        <v>22330051920191</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6230,16 +5510,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920188</v>
+        <v>22330051920192</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6247,16 +5527,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920187</v>
+        <v>22330051920196</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6264,16 +5544,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920191</v>
+        <v>22330051920197</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6281,16 +5558,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920192</v>
+        <v>22330051920358</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6298,16 +5575,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920197</v>
+        <v>22330051920356</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
         <v>142</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -6318,13 +5595,13 @@
         <v>22330051920198</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6335,13 +5612,13 @@
         <v>22330051920203</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6363,22 +5640,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6386,45 +5663,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920193</v>
+        <v>22330051920378</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920193</v>
+        <v>22330051920378</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6432,19 +5709,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920180</v>
+        <v>22330051920359</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
@@ -6455,68 +5732,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920180</v>
+        <v>22330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920390</v>
+        <v>22330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920390</v>
+        <v>22330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6524,45 +5801,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920199</v>
+        <v>22330051920390</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920199</v>
+        <v>22330051920390</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6570,45 +5847,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920200</v>
+        <v>22330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920200</v>
+        <v>22330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6619,88 +5896,88 @@
         <v>22330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920378</v>
+        <v>22330051920358</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920196</v>
+        <v>22330051920356</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920358</v>
+        <v>22330051920180</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6708,22 +5985,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920356</v>
+        <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -6731,22 +6008,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920363</v>
+        <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>-1</v>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -1028,7 +1028,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1064,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1105,7 +1105,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1182,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1336,7 +1336,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1413,7 +1413,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1567,7 +1567,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1644,7 +1644,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1680,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1721,7 +1721,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1757,7 +1757,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1798,7 +1798,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1875,7 +1875,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1911,7 +1911,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1952,7 +1952,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2183,7 +2183,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2219,7 +2219,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2527,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2604,7 +2604,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2876,7 +2876,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2953,7 +2953,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2989,7 +2989,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3030,7 +3030,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3066,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3184,7 +3184,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3338,7 +3338,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3374,7 +3374,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3800,7 +3800,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3978,19 +3978,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>56.41</v>
+        <v>51.28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>17</v>
@@ -5631,7 +5631,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5709,68 +5709,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920193</v>
+        <v>22330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5778,16 +5778,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920193</v>
+        <v>22330051920356</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5796,7 +5796,7 @@
         <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5939,39 +5939,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920356</v>
+        <v>22330051920180</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920180</v>
+        <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -5985,47 +5985,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920363</v>
+        <v>22330051920200</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -152,7 +152,7 @@
     <t>TZOMPOLE COLOHUA JOSE LEONARDO</t>
   </si>
   <si>
-    <t>VAZQUEZ COLOHUA NAHUM HIRAM</t>
+    <t>VASQUEZ COLOHUA NAHUM HIRAM</t>
   </si>
   <si>
     <t>VERA GONZALEZ ISRAEL</t>
@@ -266,7 +266,7 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>VERA</t>
@@ -1863,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -2402,7 +2402,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -2438,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2479,7 +2479,7 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>9</v>
@@ -3018,7 +3018,7 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -3054,7 +3054,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -3095,7 +3095,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -3131,7 +3131,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>11</v>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -1025,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -1102,7 +1102,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1179,7 +1179,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1333,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>7</v>
@@ -1410,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1564,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1641,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1718,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1795,7 +1795,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1872,7 +1872,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1908,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1949,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -2026,7 +2026,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2103,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2216,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2257,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2411,7 +2411,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2488,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2565,7 +2565,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2642,7 +2642,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2719,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2796,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2873,7 +2873,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2950,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -3063,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3104,7 +3104,7 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3140,7 +3140,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3335,7 +3335,7 @@
         <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -3371,7 +3371,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3412,7 +3412,7 @@
         <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3448,7 +3448,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>-1</v>
@@ -3489,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3525,7 +3525,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>-1</v>
@@ -3560,13 +3560,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3596,7 +3596,7 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3643,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3679,7 +3679,7 @@
         <v>6</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -3720,7 +3720,7 @@
         <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3797,7 +3797,7 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>9</v>
@@ -3865,7 +3865,7 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>6</v>
@@ -3874,7 +3874,7 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3901,7 +3901,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>5</v>
@@ -3910,7 +3910,7 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>-1</v>
@@ -4010,16 +4010,16 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="G3">
-        <v>41.03</v>
+        <v>43.59</v>
       </c>
       <c r="H3">
         <v>6.2</v>
@@ -4042,16 +4042,16 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>71.79000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
         <v>9.1</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>3</v>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -251,259 +251,259 @@
     <t>PELLICO</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ISMAEL</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>GUSTAVO URIEL</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ISMAEL</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>CAZARES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>JOSE RAMON</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>VECKA</t>
+  </si>
+  <si>
+    <t>GERSON</t>
+  </si>
+  <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>FATIMA YAMILET</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>ABDIEL NOE</t>
   </si>
   <si>
     <t>OSMAR</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>GUSTAVO URIEL</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>JOSE RAMON</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>VECKA</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>FATIMA YAMILET</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>ARLETT</t>
@@ -1238,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1256,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1292,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -2073,7 +2073,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2127,7 +2127,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2689,7 +2689,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -2707,7 +2707,7 @@
         <v>-1</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>6</v>
@@ -3181,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -3217,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3228,7 +3228,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3240,13 +3240,13 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>-1</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3258,7 +3258,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3282,7 +3282,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3294,7 +3294,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -3536,7 +3536,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -3554,7 +3554,7 @@
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3590,7 +3590,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3690,7 +3690,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>-1</v>
@@ -3708,7 +3708,7 @@
         <v>-1</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3744,7 +3744,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3844,7 +3844,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -3862,7 +3862,7 @@
         <v>-1</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -3898,7 +3898,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>5</v>
@@ -4106,25 +4106,25 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="G6">
+        <v>10.26</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>84.62</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>15.38</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4138,25 +4138,25 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>97.44</v>
+      </c>
+      <c r="G7">
+        <v>2.56</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>92.31</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>7.69</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4201,10 +4201,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4221,10 +4221,10 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4241,10 +4241,10 @@
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4261,10 +4261,10 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4281,16 +4281,16 @@
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4301,36 +4301,36 @@
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920413</v>
+        <v>22330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4341,36 +4341,36 @@
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920388</v>
+        <v>21330051920265</v>
       </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4381,30 +4381,30 @@
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920265</v>
+        <v>22330051920378</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4415,62 +4415,62 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920378</v>
+        <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920193</v>
+        <v>22330051920194</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4481,50 +4481,50 @@
         <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920194</v>
+        <v>22330051920195</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920194</v>
+        <v>22330051920390</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -4535,16 +4535,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920195</v>
+        <v>22330051920199</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
         <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -4555,56 +4555,56 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920180</v>
+        <v>22330051920391</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
         <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920363</v>
+        <v>22330051920391</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920390</v>
+        <v>22330051920200</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -4615,56 +4615,56 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920199</v>
+        <v>22330051920371</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920391</v>
+        <v>22330051920371</v>
       </c>
       <c r="B24" t="s">
         <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920391</v>
+        <v>22330051920201</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -4675,16 +4675,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920391</v>
+        <v>22330051920201</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -4695,36 +4695,36 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920391</v>
+        <v>22330051920202</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920200</v>
+        <v>22330051920202</v>
       </c>
       <c r="B28" t="s">
         <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -4735,201 +4735,21 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920371</v>
+        <v>22330051920204</v>
       </c>
       <c r="B29" t="s">
         <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920371</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920371</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920201</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920201</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920202</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920202</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920202</v>
-      </c>
-      <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920204</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920204</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4966,101 +4786,101 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920391</v>
+        <v>22330051920389</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
         <v>99</v>
       </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920413</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920194</v>
+        <v>22330051920413</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920371</v>
+        <v>22330051920388</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920202</v>
+        <v>21330051920265</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920389</v>
+        <v>22330051920194</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5068,16 +4888,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920190</v>
+        <v>22330051920391</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5085,16 +4905,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920388</v>
+        <v>22330051920371</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -5102,16 +4922,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920265</v>
+        <v>22330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5119,16 +4939,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920201</v>
+        <v>22330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5136,33 +4956,33 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920204</v>
+        <v>22330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920378</v>
+        <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5170,16 +4990,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5187,16 +5007,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920193</v>
+        <v>22330051920195</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5204,16 +5024,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920195</v>
+        <v>22330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5221,16 +5041,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920180</v>
+        <v>22330051920199</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5238,16 +5058,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920363</v>
+        <v>22330051920200</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5255,16 +5075,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920390</v>
+        <v>22330051920204</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5272,44 +5092,44 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920199</v>
+        <v>22330051920177</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920200</v>
+        <v>22330051920178</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920177</v>
+        <v>22330051920179</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
         <v>133</v>
@@ -5323,10 +5143,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920178</v>
+        <v>22330051920181</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>134</v>
@@ -5340,13 +5160,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920179</v>
+        <v>22330051920182</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
         <v>147</v>
@@ -5357,13 +5177,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920181</v>
+        <v>22330051920183</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
         <v>148</v>
@@ -5374,13 +5194,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920182</v>
+        <v>22330051920184</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>149</v>
@@ -5391,13 +5211,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920183</v>
+        <v>22330051920185</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>150</v>
@@ -5408,13 +5228,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920184</v>
+        <v>22330051920186</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
         <v>151</v>
@@ -5425,13 +5245,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920185</v>
+        <v>22330051920188</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
         <v>152</v>
@@ -5442,13 +5262,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920186</v>
+        <v>22330051920187</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
         <v>153</v>
@@ -5459,13 +5279,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920188</v>
+        <v>22330051920191</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
         <v>154</v>
@@ -5476,13 +5296,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920187</v>
+        <v>22330051920192</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>155</v>
@@ -5493,13 +5313,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920191</v>
+        <v>22330051920196</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
         <v>156</v>
@@ -5510,13 +5330,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920192</v>
+        <v>22330051920197</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>157</v>
@@ -5527,13 +5344,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920196</v>
+        <v>22330051920358</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
         <v>158</v>
@@ -5544,10 +5361,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920197</v>
+        <v>22330051920356</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="C36" t="s">
+        <v>140</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
@@ -5558,13 +5378,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920358</v>
+        <v>22330051920180</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
         <v>160</v>
@@ -5575,13 +5395,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920356</v>
+        <v>22330051920363</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>161</v>
@@ -5595,10 +5415,10 @@
         <v>22330051920198</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
         <v>162</v>
@@ -5612,10 +5432,10 @@
         <v>22330051920203</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
         <v>163</v>
@@ -5631,7 +5451,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5669,10 +5489,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5692,10 +5512,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5715,10 +5535,10 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5738,10 +5558,10 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5758,13 +5578,13 @@
         <v>22330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5781,13 +5601,13 @@
         <v>22330051920356</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5804,13 +5624,13 @@
         <v>22330051920390</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -5827,13 +5647,13 @@
         <v>22330051920390</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5850,13 +5670,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5873,13 +5693,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5899,10 +5719,10 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5919,13 +5739,13 @@
         <v>22330051920358</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5939,70 +5759,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920180</v>
+        <v>22330051920200</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920363</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920200</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -197,21 +197,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
@@ -227,9 +227,27 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -242,15 +260,42 @@
     <t>MARQUEZ</t>
   </si>
   <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
@@ -269,39 +314,72 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>CAZARES</t>
+  </si>
+  <si>
     <t>LAGUNA</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
     <t>TIZA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -311,15 +389,48 @@
     <t>TAPIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>XICALHUA</t>
   </si>
   <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>JOSE RAMON</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>VECKA</t>
+  </si>
+  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
+    <t>GERSON</t>
+  </si>
+  <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>FATIMA YAMILET</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
     <t>ARACELY</t>
   </si>
   <si>
@@ -338,15 +449,42 @@
     <t>CRISTIAN OSMAR</t>
   </si>
   <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>JESUS ISMAEL</t>
   </si>
   <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
     <t>JESUS IVAN</t>
   </si>
   <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>ARLETT</t>
+  </si>
+  <si>
     <t>LUIS</t>
   </si>
   <si>
@@ -368,148 +506,10 @@
     <t>ERIK</t>
   </si>
   <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>JOSE RAMON</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>VECKA</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>FATIMA YAMILET</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>ARLETT</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
   </si>
 </sst>
 </file>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1472,13 +1472,13 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1490,7 +1490,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1514,7 +1514,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1999,7 +1999,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -2011,13 +2011,13 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -2029,7 +2029,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2053,7 +2053,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2065,7 +2065,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2076,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -2088,13 +2088,13 @@
         <v>7</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -2106,7 +2106,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2130,7 +2130,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2142,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2207,7 +2207,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -2242,13 +2242,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2260,7 +2260,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2284,7 +2284,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2296,7 +2296,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2307,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2319,13 +2319,13 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2337,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2361,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2373,7 +2373,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -2414,7 +2414,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2627,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -2645,7 +2645,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2681,7 +2681,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2692,7 +2692,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -2704,13 +2704,13 @@
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2722,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2746,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2758,7 +2758,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2781,7 +2781,7 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -2799,7 +2799,7 @@
         <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -3089,7 +3089,7 @@
         <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -3107,7 +3107,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3231,7 +3231,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -3243,13 +3243,13 @@
         <v>5</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3285,7 +3285,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3297,7 +3297,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3397,7 +3397,7 @@
         <v>6</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -3415,7 +3415,7 @@
         <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3474,7 +3474,7 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -3492,7 +3492,7 @@
         <v>7</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3528,7 +3528,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3539,7 +3539,7 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -3551,16 +3551,16 @@
         <v>8</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>6</v>
@@ -3569,7 +3569,7 @@
         <v>8</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3593,10 +3593,10 @@
         <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3605,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -3628,13 +3628,13 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -3646,7 +3646,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3682,7 +3682,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3693,7 +3693,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3705,13 +3705,13 @@
         <v>6</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3723,7 +3723,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3747,7 +3747,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -3759,7 +3759,7 @@
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3859,7 +3859,7 @@
         <v>8</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3877,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3913,7 +3913,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -3978,30 +3978,30 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>51.28</v>
+        <v>58.97</v>
       </c>
       <c r="G2">
-        <v>5.13</v>
+        <v>41.03</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>43.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -4010,19 +4010,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>56.41</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G3">
-        <v>43.59</v>
+        <v>35.9</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4042,30 +4042,30 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>69.23</v>
+        <v>82.05</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>17.95</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>28.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4074,19 +4074,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>82.05</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G5">
-        <v>17.95</v>
+        <v>10.26</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4118,7 +4118,7 @@
         <v>10.26</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4191,566 +4191,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920389</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920389</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920190</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920190</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920413</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920413</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920388</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920388</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920265</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920265</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920378</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920193</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920194</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920194</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920195</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920390</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920199</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920391</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920391</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920200</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920371</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920371</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920201</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920201</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920202</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920202</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920204</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4786,319 +4226,319 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920389</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>22330051920178</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920413</v>
+        <v>22330051920179</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920388</v>
+        <v>22330051920181</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920265</v>
+        <v>22330051920182</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920194</v>
+        <v>22330051920389</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920391</v>
+        <v>22330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920371</v>
+        <v>22330051920184</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920201</v>
+        <v>22330051920185</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920202</v>
+        <v>22330051920186</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920378</v>
+        <v>22330051920188</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920359</v>
+        <v>22330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920193</v>
+        <v>22330051920190</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920195</v>
+        <v>22330051920413</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920390</v>
+        <v>22330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920199</v>
+        <v>21330051920265</v>
       </c>
       <c r="B17" t="s">
         <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920200</v>
+        <v>22330051920378</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920204</v>
+        <v>22330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920177</v>
+        <v>22330051920191</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>143</v>
@@ -5109,13 +4549,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920178</v>
+        <v>22330051920192</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>144</v>
@@ -5126,13 +4566,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920179</v>
+        <v>22330051920193</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
         <v>145</v>
@@ -5143,13 +4583,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920181</v>
+        <v>22330051920194</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5160,13 +4600,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920182</v>
+        <v>22330051920196</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>147</v>
@@ -5177,13 +4617,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920183</v>
+        <v>22330051920195</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>148</v>
@@ -5194,13 +4634,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920184</v>
+        <v>22330051920197</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
         <v>149</v>
@@ -5211,13 +4648,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920185</v>
+        <v>22330051920358</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>150</v>
@@ -5228,13 +4665,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920186</v>
+        <v>22330051920356</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>151</v>
@@ -5245,13 +4682,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920188</v>
+        <v>22330051920180</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>152</v>
@@ -5262,13 +4699,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920187</v>
+        <v>22330051920363</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
         <v>153</v>
@@ -5279,13 +4716,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920191</v>
+        <v>22330051920198</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>154</v>
@@ -5296,10 +4733,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920192</v>
+        <v>22330051920390</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
         <v>120</v>
@@ -5313,13 +4750,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920196</v>
+        <v>22330051920199</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>156</v>
@@ -5330,10 +4767,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920197</v>
+        <v>22330051920391</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>94</v>
+      </c>
+      <c r="C34" t="s">
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>157</v>
@@ -5344,13 +4784,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920358</v>
+        <v>22330051920200</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>158</v>
@@ -5361,13 +4801,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920356</v>
+        <v>22330051920371</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
@@ -5378,13 +4818,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920180</v>
+        <v>22330051920201</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
         <v>160</v>
@@ -5395,13 +4835,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920363</v>
+        <v>22330051920202</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
         <v>161</v>
@@ -5412,13 +4852,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920198</v>
+        <v>22330051920203</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
         <v>162</v>
@@ -5429,13 +4869,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920203</v>
+        <v>22330051920204</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
         <v>163</v>
@@ -5451,7 +4891,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5483,22 +4923,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920378</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5506,45 +4946,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920378</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920193</v>
+        <v>22330051920413</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5552,45 +4992,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920193</v>
+        <v>22330051920413</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920356</v>
+        <v>22330051920388</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5598,22 +5038,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920356</v>
+        <v>22330051920388</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5621,22 +5061,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920390</v>
+        <v>22330051920378</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5644,45 +5084,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920390</v>
+        <v>22330051920378</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920199</v>
+        <v>22330051920359</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5690,45 +5130,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920199</v>
+        <v>22330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920181</v>
+        <v>22330051920356</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5736,19 +5176,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920358</v>
+        <v>22330051920356</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -5759,25 +5199,255 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>22330051920390</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920390</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920201</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920201</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920181</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920193</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920358</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920199</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>22330051920200</v>
       </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B22" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920371</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
         <v>59</v>
       </c>
-      <c r="G14">
-        <v>-1</v>
+      <c r="G24">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -197,22 +197,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
+    <t>Miguel Lopez Yadira</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
-    <t>Miguel Lopez Yadira</t>
   </si>
   <si>
     <t>NC</t>
@@ -1037,10 +1037,10 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1114,10 +1114,10 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1191,10 +1191,10 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1268,10 +1268,10 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1345,10 +1345,10 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1363,10 +1363,10 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1422,10 +1422,10 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1440,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1499,10 +1499,10 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1520,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1576,10 +1576,10 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1594,7 +1594,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1653,10 +1653,10 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1671,7 +1671,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1730,10 +1730,10 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1807,10 +1807,10 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1884,10 +1884,10 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1961,10 +1961,10 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1979,10 +1979,10 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2038,10 +2038,10 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2115,10 +2115,10 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2133,10 +2133,10 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2192,10 +2192,10 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2213,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2269,10 +2269,10 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2287,7 +2287,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2346,10 +2346,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2364,10 +2364,10 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2423,10 +2423,10 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2500,10 +2500,10 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2577,10 +2577,10 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2654,10 +2654,10 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2672,10 +2672,10 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2731,10 +2731,10 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2752,7 +2752,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2808,10 +2808,10 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2826,10 +2826,10 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2885,10 +2885,10 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2903,10 +2903,10 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2962,10 +2962,10 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2980,10 +2980,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3039,10 +3039,10 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3116,10 +3116,10 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3137,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3193,10 +3193,10 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3270,10 +3270,10 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3347,10 +3347,10 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3368,7 +3368,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3424,10 +3424,10 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3501,10 +3501,10 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3522,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3578,10 +3578,10 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3599,7 +3599,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3655,10 +3655,10 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3732,10 +3732,10 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3750,10 +3750,10 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>6</v>
@@ -3809,10 +3809,10 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3827,10 +3827,10 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3886,10 +3886,10 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3904,10 +3904,10 @@
         <v>5</v>
       </c>
       <c r="V41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -3978,19 +3978,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>58.97</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G2">
-        <v>41.03</v>
+        <v>35.9</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -4010,19 +4010,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>64.09999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="G3">
-        <v>35.9</v>
+        <v>20.51</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4042,19 +4042,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>82.05</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G4">
-        <v>17.95</v>
+        <v>10.26</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4086,7 +4086,7 @@
         <v>10.26</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4106,19 +4106,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>89.73999999999999</v>
+        <v>97.44</v>
       </c>
       <c r="G6">
-        <v>10.26</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -4138,19 +4138,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>97.44</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4891,7 +4891,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4938,7 +4938,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4961,7 +4961,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920413</v>
+        <v>21330051920265</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4992,22 +4992,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920413</v>
+        <v>21330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5015,22 +5015,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920388</v>
+        <v>22330051920378</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5038,22 +5038,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920388</v>
+        <v>22330051920378</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5061,22 +5061,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920378</v>
+        <v>22330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5084,22 +5084,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920378</v>
+        <v>22330051920356</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5107,22 +5107,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920359</v>
+        <v>22330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920359</v>
+        <v>22330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5153,19 +5153,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920356</v>
+        <v>22330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>59</v>
@@ -5176,22 +5176,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920356</v>
+        <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5199,22 +5199,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920390</v>
+        <v>22330051920195</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5237,7 +5237,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5245,22 +5245,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920201</v>
+        <v>22330051920199</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
         <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5268,22 +5268,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920201</v>
+        <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5291,162 +5291,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920181</v>
+        <v>22330051920371</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920193</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920358</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>150</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920199</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920200</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920371</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920202</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" t="s">
-        <v>161</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -1034,7 +1034,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>9</v>
@@ -1043,10 +1043,10 @@
         <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -1111,7 +1111,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>8</v>
@@ -1120,10 +1120,10 @@
         <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1188,7 +1188,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>9</v>
@@ -1197,10 +1197,10 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1265,7 +1265,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1274,10 +1274,10 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1295,7 +1295,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1342,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1351,10 +1351,10 @@
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1419,7 +1419,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>9</v>
@@ -1428,10 +1428,10 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1449,7 +1449,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1496,7 +1496,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -1505,10 +1505,10 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1573,7 +1573,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>10</v>
@@ -1582,16 +1582,16 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1600,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1650,7 +1650,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1659,16 +1659,16 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1727,7 +1727,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>9</v>
@@ -1736,10 +1736,10 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1804,7 +1804,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1813,10 +1813,10 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1834,7 +1834,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1881,7 +1881,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>8</v>
@@ -1890,10 +1890,10 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1908,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1958,7 +1958,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -1967,10 +1967,10 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2035,7 +2035,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -2044,16 +2044,16 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>7</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2112,7 +2112,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>8</v>
@@ -2121,10 +2121,10 @@
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2142,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2189,7 +2189,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -2198,16 +2198,16 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2219,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2275,16 +2275,16 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2343,7 +2343,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -2352,10 +2352,10 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2420,7 +2420,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>4</v>
@@ -2429,16 +2429,16 @@
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>8</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2447,7 +2447,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2497,7 +2497,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>10</v>
@@ -2506,10 +2506,10 @@
         <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2574,7 +2574,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>9</v>
@@ -2583,10 +2583,10 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2604,7 +2604,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2651,7 +2651,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -2660,10 +2660,10 @@
         <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2728,7 +2728,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>4</v>
@@ -2737,16 +2737,16 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2805,7 +2805,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -2814,16 +2814,16 @@
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>6</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2882,7 +2882,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>9</v>
@@ -2891,10 +2891,10 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2959,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>10</v>
@@ -2968,16 +2968,16 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2986,7 +2986,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3036,7 +3036,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -3045,10 +3045,10 @@
         <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3113,7 +3113,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3122,16 +3122,16 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3190,7 +3190,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>7</v>
@@ -3199,16 +3199,16 @@
         <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>8</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -3220,7 +3220,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3267,7 +3267,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>7</v>
@@ -3276,10 +3276,10 @@
         <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>5</v>
@@ -3344,7 +3344,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -3353,10 +3353,10 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3421,7 +3421,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -3430,16 +3430,16 @@
         <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>7</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3498,7 +3498,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>6</v>
@@ -3507,16 +3507,16 @@
         <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>8</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3528,7 +3528,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3575,7 +3575,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>8</v>
@@ -3584,10 +3584,10 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3605,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3652,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>7</v>
@@ -3661,16 +3661,16 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>7</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3682,7 +3682,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3729,7 +3729,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -3738,16 +3738,16 @@
         <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>7</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -3806,7 +3806,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>10</v>
@@ -3815,16 +3815,16 @@
         <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>9</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3836,7 +3836,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3883,7 +3883,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
         <v>8</v>
@@ -3892,16 +3892,16 @@
         <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -3978,19 +3978,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>64.09999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="G2">
-        <v>35.9</v>
+        <v>23.08</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4074,16 +4074,16 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="G5">
-        <v>10.26</v>
+        <v>7.69</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -4118,7 +4118,7 @@
         <v>2.56</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4891,7 +4891,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5061,22 +5061,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920356</v>
+        <v>22330051920204</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5084,16 +5084,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920356</v>
+        <v>22330051920204</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5107,22 +5107,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920201</v>
+        <v>22330051920388</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5130,16 +5130,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920201</v>
+        <v>22330051920195</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5153,22 +5153,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920388</v>
+        <v>22330051920356</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5176,22 +5176,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920359</v>
+        <v>22330051920199</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5199,22 +5199,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920195</v>
+        <v>22330051920371</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5222,93 +5222,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920390</v>
+        <v>22330051920201</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920199</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920371</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20221.xlsx
+++ b/grupos/1AV - Estadisticos 20221.xlsx
@@ -1031,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -1108,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -1126,7 +1126,7 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1185,7 +1185,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1339,7 +1339,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1493,7 +1493,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1511,7 +1511,7 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1647,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -1724,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1801,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1878,7 +1878,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1896,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2109,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2186,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2204,7 +2204,7 @@
         <v>7</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2263,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2417,7 +2417,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2435,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2494,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2571,7 +2571,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2648,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2725,7 +2725,7 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -2802,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2820,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2879,7 +2879,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2897,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>7</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -3033,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3051,7 +3051,7 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3110,7 +3110,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>10</v>
@@ -3187,7 +3187,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>8</v>
@@ -3264,7 +3264,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3341,7 +3341,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3418,7 +3418,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -3436,7 +3436,7 @@
         <v>8</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3495,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -3513,7 +3513,7 @@
         <v>7</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>10</v>
@@ -3649,7 +3649,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -3667,7 +3667,7 @@
         <v>7</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3726,7 +3726,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -3803,7 +3803,7 @@
         <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3821,7 +3821,7 @@
         <v>7</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>9</v>
@@ -3880,7 +3880,7 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>8</v>
@@ -3898,7 +3898,7 @@
         <v>5</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>6</v>
@@ -4054,7 +4054,7 @@
         <v>10.26</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920204</v>
+        <v>22330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5084,16 +5084,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920204</v>
+        <v>22330051920195</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920195</v>
+        <v>22330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5153,16 +5153,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920356</v>
+        <v>22330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5176,22 +5176,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920199</v>
+        <v>22330051920371</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5199,22 +5199,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920371</v>
+        <v>22330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5222,22 +5222,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920201</v>
+        <v>22330051920204</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
